--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.71009</v>
+        <v>16.99988</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60442</v>
+        <v>16.64755</v>
       </c>
       <c r="E2" t="n">
-        <v>17.02883</v>
+        <v>16.91971</v>
       </c>
       <c r="F2" t="n">
-        <v>41.77792</v>
+        <v>42.54725</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05095</v>
+        <v>0.04982</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82424</v>
+        <v>1.80803</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.81456</v>
+        <v>16.65764</v>
       </c>
       <c r="D3" t="n">
-        <v>16.93061</v>
+        <v>16.63799</v>
       </c>
       <c r="E3" t="n">
-        <v>16.37321</v>
+        <v>16.63862</v>
       </c>
       <c r="F3" t="n">
-        <v>42.54947</v>
+        <v>42.45726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05078</v>
+        <v>0.05003</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80354</v>
+        <v>1.8347</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81947</v>
+        <v>16.99134</v>
       </c>
       <c r="D4" t="n">
-        <v>16.53187</v>
+        <v>16.38252</v>
       </c>
       <c r="E4" t="n">
-        <v>16.68892</v>
+        <v>16.39982</v>
       </c>
       <c r="F4" t="n">
-        <v>42.24291</v>
+        <v>42.88756</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05123</v>
+        <v>0.05096</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81778</v>
+        <v>1.81638</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.86676</v>
+        <v>17.21076</v>
       </c>
       <c r="D5" t="n">
-        <v>16.25567</v>
+        <v>16.44651</v>
       </c>
       <c r="E5" t="n">
-        <v>16.78182</v>
+        <v>16.90117</v>
       </c>
       <c r="F5" t="n">
-        <v>42.51334</v>
+        <v>42.3698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05098</v>
+        <v>0.0504</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82646</v>
+        <v>1.82863</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.86533</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.15622</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.52263</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42.69337</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.81887</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71185</v>
+        <v>16.96271</v>
       </c>
       <c r="D7" t="n">
-        <v>16.69247</v>
+        <v>16.47982</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46352</v>
+        <v>16.77365</v>
       </c>
       <c r="F7" t="n">
-        <v>42.51654</v>
+        <v>42.56969</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0509</v>
+        <v>0.05025</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82985</v>
+        <v>1.82837</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.56304</v>
+        <v>17.09259</v>
       </c>
       <c r="D8" t="n">
-        <v>16.51267</v>
+        <v>16.24243</v>
       </c>
       <c r="E8" t="n">
-        <v>16.95469</v>
+        <v>16.98417</v>
       </c>
       <c r="F8" t="n">
-        <v>42.93098</v>
+        <v>42.06605</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05092</v>
+        <v>0.05155</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81826</v>
+        <v>1.84075</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.00764</v>
+        <v>16.865</v>
       </c>
       <c r="D9" t="n">
-        <v>16.50152</v>
+        <v>16.53881</v>
       </c>
       <c r="E9" t="n">
-        <v>16.8848</v>
+        <v>16.54823</v>
       </c>
       <c r="F9" t="n">
-        <v>43.01174</v>
+        <v>42.91823</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05158</v>
+        <v>0.05092</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8161</v>
+        <v>1.83682</v>
       </c>
     </row>
     <row r="10">
@@ -647,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.8163</v>
+        <v>17.2779</v>
       </c>
       <c r="D10" t="n">
-        <v>16.34195</v>
+        <v>16.19476</v>
       </c>
       <c r="E10" t="n">
-        <v>16.57363</v>
+        <v>16.86718</v>
       </c>
       <c r="F10" t="n">
-        <v>42.09613</v>
+        <v>42.30585</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05073</v>
+        <v>0.05066</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8172</v>
+        <v>1.80559</v>
       </c>
     </row>
     <row r="11">
@@ -683,12 +696,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.67964</v>
+        <v>17.03613</v>
       </c>
       <c r="D12" t="n">
-        <v>15.80951</v>
+        <v>16.36362</v>
       </c>
       <c r="E12" t="n">
-        <v>16.5123</v>
+        <v>16.77034</v>
       </c>
       <c r="F12" t="n">
-        <v>21.24074</v>
+        <v>42.53768</v>
       </c>
       <c r="G12" t="n">
-        <v>33.76397</v>
+        <v>0.05042</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81674</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.99134</v>
+        <v>16.63884</v>
       </c>
       <c r="D13" t="n">
-        <v>16.13389</v>
+        <v>16.47762</v>
       </c>
       <c r="E13" t="n">
-        <v>16.51265</v>
+        <v>16.59274</v>
       </c>
       <c r="F13" t="n">
-        <v>21.69566</v>
+        <v>42.54247</v>
       </c>
       <c r="G13" t="n">
-        <v>35.0436</v>
+        <v>0.05016</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.81526</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +771,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.54679</v>
+        <v>16.76386</v>
       </c>
       <c r="D14" t="n">
-        <v>16.18416</v>
+        <v>16.61433</v>
       </c>
       <c r="E14" t="n">
-        <v>16.34264</v>
+        <v>16.71658</v>
       </c>
       <c r="F14" t="n">
-        <v>21.67002</v>
+        <v>42.38152</v>
       </c>
       <c r="G14" t="n">
-        <v>34.33756</v>
+        <v>0.04988</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.82916</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.4231</v>
+        <v>17.02864</v>
       </c>
       <c r="D15" t="n">
-        <v>15.56514</v>
+        <v>16.55103</v>
       </c>
       <c r="E15" t="n">
-        <v>16.55869</v>
+        <v>16.8905</v>
       </c>
       <c r="F15" t="n">
-        <v>21.85494</v>
+        <v>42.30074</v>
       </c>
       <c r="G15" t="n">
-        <v>34.19007</v>
+        <v>0.05096</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.78675</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.67299</v>
+        <v>16.95634</v>
       </c>
       <c r="D16" t="n">
-        <v>16.14523</v>
+        <v>16.51455</v>
       </c>
       <c r="E16" t="n">
-        <v>16.27885</v>
+        <v>16.74318</v>
       </c>
       <c r="F16" t="n">
-        <v>21.85657</v>
+        <v>42.26645</v>
       </c>
       <c r="G16" t="n">
-        <v>34.25847</v>
+        <v>0.0494</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.8229</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.58185</v>
+        <v>16.94621</v>
       </c>
       <c r="D17" t="n">
-        <v>16.04899</v>
+        <v>16.59491</v>
       </c>
       <c r="E17" t="n">
-        <v>16.68072</v>
+        <v>16.76813</v>
       </c>
       <c r="F17" t="n">
-        <v>21.29343</v>
+        <v>42.70635</v>
       </c>
       <c r="G17" t="n">
-        <v>34.79182</v>
+        <v>0.05048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.82937</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.52595</v>
+        <v>16.84724</v>
       </c>
       <c r="D18" t="n">
-        <v>16.2888</v>
+        <v>16.64514</v>
       </c>
       <c r="E18" t="n">
-        <v>16.56674</v>
+        <v>16.80762</v>
       </c>
       <c r="F18" t="n">
-        <v>21.42075</v>
+        <v>41.83396</v>
       </c>
       <c r="G18" t="n">
-        <v>34.1055</v>
+        <v>0.04994</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.83043</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.865</v>
+        <v>16.84061</v>
       </c>
       <c r="D19" t="n">
-        <v>16.14543</v>
+        <v>16.51086</v>
       </c>
       <c r="E19" t="n">
-        <v>16.49769</v>
+        <v>16.66664</v>
       </c>
       <c r="F19" t="n">
-        <v>21.93984</v>
+        <v>43.69438</v>
       </c>
       <c r="G19" t="n">
-        <v>34.34402</v>
+        <v>0.05011</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82558</v>
       </c>
     </row>
     <row r="20">
@@ -885,60 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.29351</v>
+        <v>16.92266</v>
       </c>
       <c r="D20" t="n">
-        <v>16.54489</v>
+        <v>16.56609</v>
       </c>
       <c r="E20" t="n">
-        <v>16.31797</v>
+        <v>16.67034</v>
       </c>
       <c r="F20" t="n">
-        <v>21.78545</v>
+        <v>42.72916</v>
       </c>
       <c r="G20" t="n">
-        <v>33.90499</v>
+        <v>0.05044</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.74695</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -950,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.75944</v>
+        <v>15.98526</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07982</v>
+        <v>15.58779</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60983</v>
+        <v>15.71884</v>
       </c>
       <c r="F22" t="n">
-        <v>0.96216</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10891</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09132</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12682</v>
+        <v>255.84976</v>
       </c>
     </row>
     <row r="23">
@@ -985,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.74416</v>
+        <v>15.95397</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08103</v>
+        <v>15.38767</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60186</v>
+        <v>15.71916</v>
       </c>
       <c r="F23" t="n">
-        <v>0.95806</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10876</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09347</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12614</v>
+        <v>256.83377</v>
       </c>
     </row>
     <row r="24">
@@ -1016,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7382</v>
+        <v>15.79011</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0813</v>
+        <v>15.63548</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6105</v>
+        <v>15.64131</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95875</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11146</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09377000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12408</v>
+        <v>256.86729</v>
       </c>
     </row>
     <row r="25">
@@ -1047,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75589</v>
+        <v>15.73935</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08167000000000001</v>
+        <v>15.55145</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60053</v>
+        <v>15.65504</v>
       </c>
       <c r="F25" t="n">
-        <v>0.95603</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.10671</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09293</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12649</v>
+        <v>255.16308</v>
       </c>
     </row>
     <row r="26">
@@ -1078,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.76001</v>
+        <v>15.7412</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08135000000000001</v>
+        <v>15.48535</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60577</v>
+        <v>15.5891</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9655</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10961</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09372</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12451</v>
+        <v>253.31885</v>
       </c>
     </row>
     <row r="27">
@@ -1109,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.73913</v>
+        <v>15.69705</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08135000000000001</v>
+        <v>15.53338</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60241</v>
+        <v>15.68327</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95642</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11023</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09221</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12678</v>
+        <v>251.11601</v>
       </c>
     </row>
     <row r="28">
@@ -1140,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7543800000000001</v>
+        <v>15.57666</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08081000000000001</v>
+        <v>15.48914</v>
       </c>
       <c r="E28" t="n">
-        <v>0.60619</v>
+        <v>15.54233</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96649</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10894</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00728</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09488000000000001</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12652</v>
+        <v>256.71857</v>
       </c>
     </row>
     <row r="29">
@@ -1171,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75288</v>
+        <v>15.74892</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08142000000000001</v>
+        <v>15.37277</v>
       </c>
       <c r="E29" t="n">
-        <v>0.61757</v>
+        <v>15.44061</v>
       </c>
       <c r="F29" t="n">
-        <v>0.94924</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10988</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09279999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12696</v>
+        <v>257.43367</v>
       </c>
     </row>
     <row r="30">
@@ -1202,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.75629</v>
+        <v>15.90093</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08173999999999999</v>
+        <v>15.77752</v>
       </c>
       <c r="E30" t="n">
-        <v>0.606</v>
+        <v>15.86361</v>
       </c>
       <c r="F30" t="n">
-        <v>0.95934</v>
-      </c>
-      <c r="G30" t="n">
+        <v>255.08614</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.52626</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.09732</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.4811</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.02707</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.38026</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.54257</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.00445</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.13071</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.70442</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.95914</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.88159</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.74407</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.53572</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.8278</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.05415</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.44112</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.96579</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.24669</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.79077</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.75431</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.7045</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.85489</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.33285</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.02214</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.11544</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.53264</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.92109</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.34927</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.03371</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.52963</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.5914</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.59394</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.36167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.68883</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.92169</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.76885</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.97257</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.47193</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.83306</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.18168</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.69618</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.1343</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.64133</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.29541</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.97454</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.55145</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.97678</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.28886</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.74334</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.67674</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.5834</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.46464</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.50699</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.77752</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.83136</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.74981</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.3468</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.35213</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.66609</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.05416</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.9357</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.04782</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.70298</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.91144</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.43733</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.77432</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.77691</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.4066</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.67223</v>
+      </c>
+      <c r="G46" t="n">
+        <v>33.36486</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.72659</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.80991</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.40363</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.93147</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.03092</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.62156</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.70828</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.20223</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.70192</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.23568</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.62221</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.15165</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.39985</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.41483</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.31789</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.75679</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.3101</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.3918</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.87884</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.81818</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.59883</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.12968</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.61861</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.11397</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6091299999999999</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.12572</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.60581</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.13191</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61255</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.13427</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.61752</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.11517</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6022999999999999</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.12207</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60165</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.09763</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.60522</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.10304</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.59797</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.09653</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.5954</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.11492</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.59841</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.10394</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.59331</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.12249</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60448</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.10992</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.61766</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.10149</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.6015</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.12555</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.59453</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.10161</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60565</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.11613</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.75783</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08167000000000001</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6261100000000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.97656</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11003</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09404999999999999</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12659</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.75535</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.07992</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.61208</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.95523</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11136</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09236999999999999</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12627</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.7714299999999999</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08103</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.61207</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.95083</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09341000000000001</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12583</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.76478</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.07996</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61634</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.96219</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11034</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.08846999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12698</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.75985</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11145</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09447999999999999</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.1292</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.75803</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08068</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.96009</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11052</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09273000000000001</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12897</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.76051</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.62564</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.9741300000000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10987</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12545</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.74857</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08064</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.60349</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.96712</v>
+      </c>
+      <c r="G79" t="n">
         <v>0.11002</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09343</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12653</v>
+      <c r="H79" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12668</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.74268</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08203000000000001</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.61316</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9549299999999999</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11219</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09364</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12539</v>
       </c>
     </row>
   </sheetData>
